--- a/docs/Files/EV_model/ODYM_T6_ToUsedExportRateLL_V1.0.xlsx
+++ b/docs/Files/EV_model/ODYM_T6_ToUsedExportRateLL_V1.0.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927D3DBF-A9C3-41A9-90CC-269E3E831A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97488D48-F296-4229-A935-09F1AC771D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -327,9 +327,6 @@
     <t>ODYM_T6_ToUsedExportRate</t>
   </si>
   <si>
-    <t>Waste mgt. Industries</t>
-  </si>
-  <si>
     <t>Share of after use flow going to used export</t>
   </si>
   <si>
@@ -355,6 +352,9 @@
   </si>
   <si>
     <t>ODYM_Classifications_LL</t>
+  </si>
+  <si>
+    <t>Used battery collection</t>
   </si>
 </sst>
 </file>
@@ -852,7 +852,7 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
@@ -908,7 +908,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
@@ -1006,7 +1006,7 @@
         <v>36</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
@@ -1234,13 +1234,13 @@
         <v>55</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" t="s">
         <v>100</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="E2">
         <v>0.05</v>
@@ -1255,7 +1255,7 @@
         <v>54</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -1263,13 +1263,13 @@
         <v>55</v>
       </c>
       <c r="B3" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
         <v>103</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="E3">
         <v>0.05</v>
@@ -1284,7 +1284,7 @@
         <v>54</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
